--- a/real_estate_forms/010_property_utility_referral_form--real_estate_forms.xlsx
+++ b/real_estate_forms/010_property_utility_referral_form--real_estate_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Contact E</t>
+          <t>Contact Email F</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Contact Phone</t>
+          <t>Contact Phone F</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Contact Cell</t>
+          <t>Contact Cell F</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Contact Street</t>
+          <t>Contact Street F</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Contact City</t>
+          <t>Contact City F</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
